--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -207,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -284,6 +284,22 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -651,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -800,126 +816,129 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="24" t="n"/>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="25" t="n"/>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="24" t="n"/>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B4:F4"/>
@@ -1038,82 +1057,82 @@
       <c r="A8" s="11" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="35" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="35" customHeight="1">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="35" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="35" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="35" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="35" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="35" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="8" customHeight="1"/>
+    <row r="10">
+      <c r="A10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
+    </row>
+    <row r="19"/>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -1188,7 +1207,7 @@
       <c r="A30" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A8:G8"/>
@@ -1197,7 +1216,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1703,64 +1721,64 @@
       <c r="C26" s="16" t="inlineStr"/>
       <c r="D26" s="15" t="inlineStr"/>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="26" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="27" t="n"/>
-      <c r="B30" s="27" t="n"/>
-      <c r="C30" s="27" t="n"/>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="n"/>
-    </row>
-    <row r="31" ht="50" customHeight="1">
-      <c r="A31" s="25" t="n"/>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25" t="n"/>
-      <c r="D31" s="25" t="n"/>
-      <c r="E31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="50" customHeight="1">
-      <c r="A32" s="24" t="n"/>
-      <c r="B32" s="24" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-    </row>
-    <row r="33" ht="50" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="25" t="n"/>
-      <c r="D33" s="25" t="n"/>
-      <c r="E33" s="25" t="n"/>
-    </row>
-    <row r="34" ht="50" customHeight="1">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="24" t="n"/>
-    </row>
-    <row r="35" ht="50" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="25" t="n"/>
-      <c r="D35" s="25" t="n"/>
-      <c r="E35" s="25" t="n"/>
-    </row>
-    <row r="36" ht="50" customHeight="1">
-      <c r="A36" s="24" t="n"/>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-    </row>
-    <row r="37" ht="50" customHeight="1">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="34" t="n"/>
+      <c r="E30" s="34" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="n"/>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
     </row>
     <row r="38"/>
     <row r="39"/>
@@ -1770,7 +1788,7 @@
     <row r="43"/>
     <row r="44"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
@@ -1783,7 +1801,6 @@
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1957,88 +1974,88 @@
       <c r="G14" s="9" t="inlineStr"/>
       <c r="H14" s="9" t="inlineStr"/>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="27" t="n"/>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="25" t="n"/>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="25" t="n"/>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="50" customHeight="1">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="25" t="n"/>
-    </row>
-    <row r="22" ht="50" customHeight="1">
-      <c r="A22" s="24" t="n"/>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="50" customHeight="1">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="50" customHeight="1">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="50" customHeight="1">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="25" t="n"/>
+    <row r="17">
+      <c r="A17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+      <c r="H18" s="34" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n"/>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
+      <c r="H20" s="29" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="n"/>
+      <c r="H21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="29" t="n"/>
+      <c r="H24" s="29" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
     </row>
     <row r="26"/>
     <row r="27"/>
@@ -2050,12 +2067,11 @@
     <row r="33"/>
     <row r="34"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -667,15 +667,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -872,7 +872,6 @@
       <c r="E19" s="15" t="n"/>
       <c r="F19" s="15" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="29" t="n"/>
       <c r="B21" s="29" t="n"/>
@@ -937,8 +936,6 @@
       <c r="E28" s="29" t="n"/>
       <c r="F28" s="29" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B4:F4"/>
@@ -964,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -972,7 +969,7 @@
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1017,11 +1014,6 @@
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>リスク</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
@@ -1034,7 +1026,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="9" t="n"/>
@@ -1043,7 +1034,6 @@
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6" ht="8" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
@@ -1058,165 +1048,90 @@
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10">
-      <c r="A10" s="30" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>■ 実施前確認事項</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="n"/>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="31" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>確認内容</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="22" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
+      <c r="A12" s="14" t="n"/>
       <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
+      <c r="C12" s="16" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
+      <c r="A13" s="14" t="n"/>
       <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="32" t="n"/>
-      <c r="G13" s="32" t="n"/>
+      <c r="C13" s="16" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
+      <c r="A14" s="14" t="n"/>
       <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
+      <c r="C14" s="16" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
+      <c r="A15" s="14" t="n"/>
       <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
+      <c r="C15" s="16" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="32" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>■ 懸念事項</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="A18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+    </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>■ 実施前確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>確認内容</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="15" t="inlineStr"/>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr"/>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr"/>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="16" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr"/>
-    </row>
+      <c r="A20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1"/>
+    <row r="22" ht="25" customHeight="1"/>
+    <row r="23" ht="25" customHeight="1"/>
+    <row r="24" ht="25" customHeight="1"/>
+    <row r="25" ht="25" customHeight="1"/>
     <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>■ 懸念事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="A28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="A29" s="17" t="n"/>
-    </row>
-    <row r="30" ht="35" customHeight="1">
-      <c r="A30" s="11" t="n"/>
-    </row>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="35" customHeight="1"/>
+    <row r="29" ht="35" customHeight="1"/>
+    <row r="30" ht="35" customHeight="1"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A28:G28"/>
+  <mergeCells count="10">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1398,12 +1313,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>役割</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>根拠</t>
+          <t>影響内容</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1468,11 +1383,7 @@
           <t>役割</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>調査結果</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="inlineStr"/>
     </row>
     <row r="29" ht="40" customHeight="1">
@@ -1525,14 +1436,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -1673,16 +1584,8 @@
           <t>確認内容</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -1780,13 +1683,6 @@
       <c r="D37" s="29" t="n"/>
       <c r="E37" s="29" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B4:E4"/>
@@ -1814,7 +1710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1888,11 +1784,6 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>根拠</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="6" t="n"/>
@@ -1902,7 +1793,6 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="9" t="n"/>
@@ -1912,7 +1802,6 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="inlineStr"/>
       <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="n"/>
@@ -1922,7 +1811,6 @@
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="9" t="n"/>
@@ -1932,7 +1820,6 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="inlineStr"/>
       <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="n"/>
@@ -1942,7 +1829,6 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="9" t="n"/>
@@ -1952,7 +1838,6 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="inlineStr"/>
       <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="6" t="n"/>
@@ -1962,7 +1847,6 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="9" t="n"/>
@@ -1972,7 +1856,6 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="inlineStr"/>
       <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="33" t="n"/>
@@ -1985,7 +1868,6 @@
       <c r="E18" s="34" t="n"/>
       <c r="F18" s="34" t="n"/>
       <c r="G18" s="34" t="n"/>
-      <c r="H18" s="34" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="29" t="n"/>
@@ -1995,7 +1877,6 @@
       <c r="E19" s="29" t="n"/>
       <c r="F19" s="29" t="n"/>
       <c r="G19" s="29" t="n"/>
-      <c r="H19" s="29" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="29" t="n"/>
@@ -2005,7 +1886,6 @@
       <c r="E20" s="29" t="n"/>
       <c r="F20" s="29" t="n"/>
       <c r="G20" s="29" t="n"/>
-      <c r="H20" s="29" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="n"/>
@@ -2015,7 +1895,6 @@
       <c r="E21" s="29" t="n"/>
       <c r="F21" s="29" t="n"/>
       <c r="G21" s="29" t="n"/>
-      <c r="H21" s="29" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="n"/>
@@ -2025,7 +1904,6 @@
       <c r="E22" s="29" t="n"/>
       <c r="F22" s="29" t="n"/>
       <c r="G22" s="29" t="n"/>
-      <c r="H22" s="29" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="n"/>
@@ -2035,7 +1913,6 @@
       <c r="E23" s="29" t="n"/>
       <c r="F23" s="29" t="n"/>
       <c r="G23" s="29" t="n"/>
-      <c r="H23" s="29" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="n"/>
@@ -2045,7 +1922,6 @@
       <c r="E24" s="29" t="n"/>
       <c r="F24" s="29" t="n"/>
       <c r="G24" s="29" t="n"/>
-      <c r="H24" s="29" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="n"/>
@@ -2055,23 +1931,13 @@
       <c r="E25" s="29" t="n"/>
       <c r="F25" s="29" t="n"/>
       <c r="G25" s="29" t="n"/>
-      <c r="H25" s="29" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -2085,13 +1951,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2128,17 +1994,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>変更種別</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
           <t>デプロイ方法</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
@@ -2147,16 +2003,12 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="9" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="8" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
@@ -2177,18 +2029,8 @@
           <t>確認内容</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="14" t="n"/>
@@ -2253,18 +2095,8 @@
           <t>確認内容</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="14" t="n"/>
@@ -2348,42 +2180,34 @@
           <t>結果</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="7" t="inlineStr"/>
+      <c r="D38" s="7" t="n"/>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr"/>
       <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -670,7 +670,7 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1145,10 +1145,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
@@ -1182,15 +1182,10 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>検証方法</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>検証結果</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -1201,35 +1196,30 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="9" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="28" customHeight="1">
@@ -1260,7 +1250,6 @@
           <t>説明</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -1316,12 +1305,7 @@
           <t>役割</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>影響内容</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="6" t="n"/>
@@ -1384,7 +1368,6 @@
         </is>
       </c>
       <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="inlineStr"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="6" t="n"/>
@@ -1418,11 +1401,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1436,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1468,8 +1451,7 @@
       </c>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1479,8 +1461,7 @@
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1490,8 +1471,7 @@
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
     </row>
     <row r="6" ht="8" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
@@ -1522,28 +1502,24 @@
           <t>変更概要</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="35" customHeight="1">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10" ht="35" customHeight="1">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
-      <c r="E10" s="13" t="n"/>
     </row>
     <row r="11" ht="35" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="12" t="n"/>
     </row>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="28" customHeight="1">
@@ -1586,7 +1562,6 @@
       </c>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="14" t="n"/>
@@ -1632,71 +1607,63 @@
       <c r="B30" s="34" t="n"/>
       <c r="C30" s="34" t="n"/>
       <c r="D30" s="34" t="n"/>
-      <c r="E30" s="34" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="29" t="n"/>
       <c r="B31" s="29" t="n"/>
       <c r="C31" s="29" t="n"/>
       <c r="D31" s="29" t="n"/>
-      <c r="E31" s="29" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="29" t="n"/>
       <c r="B32" s="29" t="n"/>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="n"/>
-      <c r="E32" s="29" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="n"/>
       <c r="B33" s="29" t="n"/>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="29" t="n"/>
-      <c r="E33" s="29" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="n"/>
       <c r="B34" s="29" t="n"/>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="29" t="n"/>
-      <c r="E34" s="29" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="n"/>
       <c r="B35" s="29" t="n"/>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="29" t="n"/>
-      <c r="E35" s="29" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="29" t="n"/>
       <c r="B36" s="29" t="n"/>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="29" t="n"/>
-      <c r="E36" s="29" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="29" t="n"/>
       <c r="B37" s="29" t="n"/>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="29" t="n"/>
-      <c r="E37" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -2029,8 +1996,8 @@
           <t>確認内容</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="14" t="n"/>
@@ -2095,8 +2062,8 @@
           <t>確認内容</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="14" t="n"/>
@@ -2180,7 +2147,7 @@
           <t>結果</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="22" t="n"/>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="6" t="inlineStr"/>
@@ -2189,23 +2156,26 @@
       <c r="D39" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A37:D37"/>
+  <mergeCells count="21">
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1055,11 +1055,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A11" s="7" t="n"/>
       <c r="B11" s="7" t="inlineStr">
         <is>
           <t>確認内容</t>
@@ -1550,11 +1546,7 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="inlineStr">
         <is>
           <t>確認内容</t>
@@ -1654,15 +1646,15 @@
   <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1986,11 +1978,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="inlineStr">
         <is>
           <t>確認内容</t>
@@ -2052,11 +2040,7 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="inlineStr">
         <is>
           <t>確認内容</t>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1910,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2108,39 +2108,11 @@
       <c r="A35" s="11" t="n"/>
     </row>
     <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>■ リリース実施記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>実施日</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>実施者</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="D38" s="22" t="n"/>
-    </row>
-    <row r="39" ht="25" customHeight="1">
-      <c r="A39" s="6" t="inlineStr"/>
-      <c r="B39" s="6" t="inlineStr"/>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="6" t="inlineStr"/>
-    </row>
+    <row r="37" ht="28" customHeight="1"/>
+    <row r="38" ht="28" customHeight="1"/>
+    <row r="39" ht="25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="B8:D8"/>
@@ -2153,10 +2125,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="C38:D38"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A2:D2"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -207,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +300,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -839,102 +845,6 @@
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="15" t="n"/>
       <c r="F15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="29" t="n"/>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="29" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="29" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n"/>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="29" t="n"/>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="29" t="n"/>
-      <c r="E28" s="29" t="n"/>
-      <c r="F28" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1067,28 +977,28 @@
       <c r="F11" s="22" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="15" t="inlineStr"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="35" t="inlineStr"/>
+      <c r="D12" s="36" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="15" t="inlineStr"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="35" t="inlineStr"/>
+      <c r="D13" s="36" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr"/>
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="35" t="inlineStr"/>
+      <c r="D14" s="36" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="15" t="inlineStr"/>
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="35" t="inlineStr"/>
+      <c r="D15" s="36" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1415,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1556,91 +1466,40 @@
       <c r="D20" s="7" t="n"/>
     </row>
     <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="14" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="15" t="inlineStr"/>
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="35" t="inlineStr"/>
+      <c r="D21" s="36" t="inlineStr"/>
     </row>
     <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="15" t="inlineStr"/>
+      <c r="A22" s="35" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="35" t="inlineStr"/>
+      <c r="D22" s="36" t="inlineStr"/>
     </row>
     <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr"/>
+      <c r="A23" s="35" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="35" t="inlineStr"/>
+      <c r="D23" s="36" t="inlineStr"/>
     </row>
     <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr"/>
+      <c r="A24" s="35" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="35" t="inlineStr"/>
+      <c r="D24" s="36" t="inlineStr"/>
     </row>
     <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="16" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr"/>
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="35" t="inlineStr"/>
+      <c r="D25" s="36" t="inlineStr"/>
     </row>
     <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="16" t="inlineStr"/>
-      <c r="D26" s="15" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="33" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="n"/>
-      <c r="B30" s="34" t="n"/>
-      <c r="C30" s="34" t="n"/>
-      <c r="D30" s="34" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="29" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="n"/>
-      <c r="B32" s="29" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="29" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="29" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="29" t="n"/>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="29" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="n"/>
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="29" t="n"/>
-      <c r="B36" s="29" t="n"/>
-      <c r="C36" s="29" t="n"/>
-      <c r="D36" s="29" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="29" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="29" t="n"/>
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="35" t="inlineStr"/>
+      <c r="D26" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1669,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1815,81 +1674,6 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="inlineStr"/>
       <c r="G14" s="9" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="n"/>
-      <c r="B18" s="34" t="n"/>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n"/>
-      <c r="F18" s="34" t="n"/>
-      <c r="G18" s="34" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="29" t="n"/>
-      <c r="C19" s="29" t="n"/>
-      <c r="D19" s="29" t="n"/>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="29" t="n"/>
-      <c r="G19" s="29" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="29" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="29" t="n"/>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="29" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="29" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="29" t="n"/>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="29" t="n"/>
-      <c r="G22" s="29" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="29" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="29" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1988,28 +1772,28 @@
       <c r="D8" s="22" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="15" t="inlineStr"/>
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="35" t="inlineStr"/>
+      <c r="D9" s="36" t="inlineStr"/>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="14" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="15" t="inlineStr"/>
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="35" t="inlineStr"/>
+      <c r="D10" s="36" t="inlineStr"/>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="14" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="15" t="inlineStr"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="35" t="inlineStr"/>
+      <c r="D11" s="36" t="inlineStr"/>
     </row>
     <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="14" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="15" t="inlineStr"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="35" t="inlineStr"/>
+      <c r="D12" s="36" t="inlineStr"/>
     </row>
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="28" customHeight="1">
@@ -2050,28 +1834,28 @@
       <c r="D21" s="22" t="n"/>
     </row>
     <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="15" t="inlineStr"/>
+      <c r="A22" s="35" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="35" t="inlineStr"/>
+      <c r="D22" s="36" t="inlineStr"/>
     </row>
     <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr"/>
+      <c r="A23" s="35" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="35" t="inlineStr"/>
+      <c r="D23" s="36" t="inlineStr"/>
     </row>
     <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr"/>
+      <c r="A24" s="35" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="35" t="inlineStr"/>
+      <c r="D24" s="36" t="inlineStr"/>
     </row>
     <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="16" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr"/>
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="35" t="inlineStr"/>
+      <c r="D25" s="36" t="inlineStr"/>
     </row>
     <row r="26" ht="8" customHeight="1"/>
     <row r="27" ht="28" customHeight="1">
